--- a/history_matching/examples/radius_completed/iter2/Cuts/RadiusShouldBe15/history_matching_config.xlsx
+++ b/history_matching/examples/radius_completed/iter2/Cuts/RadiusShouldBe15/history_matching_config.xlsx
@@ -1,250 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="History_Matching_Params" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Inputs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Results" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Param_Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History_Matching_Params" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Results" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Param_Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="75">
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>cut_name</t>
-  </si>
-  <si>
-    <t>RadiusShouldBe15</t>
-  </si>
-  <si>
-    <t>desired_result</t>
-  </si>
-  <si>
-    <t>desired_result_var</t>
-  </si>
-  <si>
-    <t>discrepancy_var</t>
-  </si>
-  <si>
-    <t>implausibility_threshold</t>
-  </si>
-  <si>
-    <t>iteration</t>
-  </si>
-  <si>
-    <t>training_fraction</t>
-  </si>
-  <si>
-    <t>Sample_Id</t>
-  </si>
-  <si>
-    <t>Sample</t>
-  </si>
-  <si>
-    <t>First Parameter</t>
-  </si>
-  <si>
-    <t>Second Parameter</t>
-  </si>
-  <si>
-    <t>Exp_Id</t>
-  </si>
-  <si>
-    <t>Train</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000000</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000001</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000002</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000003</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000004</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000005</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000006</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000007</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000008</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000009</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000010</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000011</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000012</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000013</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000014</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000015</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000016</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000017</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000018</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000019</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000020</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000021</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000022</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000023</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000024</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000025</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000026</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000027</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000028</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000029</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000030</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000031</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000032</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000033</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000034</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000035</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000036</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000037</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000038</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000039</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000040</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000041</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000042</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000043</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000044</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000045</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000046</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000047</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000048</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000049</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000050</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000051</t>
-  </si>
-  <si>
-    <t>Data_20180120_214437.000052</t>
-  </si>
-  <si>
-    <t>Sim_Id</t>
-  </si>
-  <si>
-    <t>Sim_Result</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -283,22 +53,89 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -591,75 +428,107 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>cut_name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RadiusShouldBe15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>implausibility_threshold</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>discrepancy_var</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>desired_result_var</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>training_fraction</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>desired_result</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>iteration</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.75</v>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>iterdir</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>/home/clorton/src/hm-phylo-test/history_matching/history_matching/examples/radius_completed/iter2</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -669,1091 +538,1339 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sample_Id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>First Parameter</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Second Parameter</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Exp_Id</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000000</t>
+        </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8497631804685568</v>
+        <v>-1.530015551635614</v>
       </c>
       <c r="D2" t="n">
-        <v>23.73824328809854</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
+        <v>26.58711988657396</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>18</v>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000001</t>
+        </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>-12.02577157496209</v>
+        <v>17.85998829896739</v>
       </c>
       <c r="D3" t="n">
-        <v>7.329832517009407</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
+        <v>30.68330356242265</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>19</v>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000002</t>
+        </is>
       </c>
       <c r="B4" t="n">
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>-26.85344877644219</v>
+        <v>2.085475351328526</v>
       </c>
       <c r="D4" t="n">
-        <v>-8.024554673998978</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
+        <v>-65.60691542419193</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>20</v>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000003</t>
+        </is>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>-41.51523604339693</v>
+        <v>12.50431272938187</v>
       </c>
       <c r="D5" t="n">
-        <v>1.695286475258826</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
+        <v>-42.43661087599205</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>21</v>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000004</t>
+        </is>
       </c>
       <c r="B6" t="n">
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.9279999012154859</v>
+        <v>7.375953366984092</v>
       </c>
       <c r="D6" t="n">
-        <v>11.59125859863062</v>
-      </c>
-      <c r="E6" t="s">
-        <v>17</v>
+        <v>-48.3387294544308</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>22</v>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000005</t>
+        </is>
       </c>
       <c r="B7" t="n">
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>14.40102347153904</v>
+        <v>-30.91215325741036</v>
       </c>
       <c r="D7" t="n">
-        <v>-13.78234962365453</v>
-      </c>
-      <c r="E7" t="s">
-        <v>17</v>
+        <v>-31.20992717534683</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000006</t>
+        </is>
       </c>
       <c r="B8" t="n">
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>12.05979556706487</v>
+        <v>-29.13412369699805</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.419547785385788</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
+        <v>-44.59155851686389</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>24</v>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000007</t>
+        </is>
       </c>
       <c r="B9" t="n">
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>8.08929013779364</v>
+        <v>-16.98745946673451</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.092869639841126</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
+        <v>-73.07534576242502</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000008</t>
+        </is>
       </c>
       <c r="B10" t="n">
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>-35.53491263899764</v>
+        <v>-3.290043702223961</v>
       </c>
       <c r="D10" t="n">
-        <v>5.957431075549025</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
+        <v>32.13230924700005</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>26</v>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000009</t>
+        </is>
       </c>
       <c r="B11" t="n">
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>-29.45294621644173</v>
+        <v>0.2390272723784861</v>
       </c>
       <c r="D11" t="n">
-        <v>4.946896342389834</v>
-      </c>
-      <c r="E11" t="s">
-        <v>17</v>
+        <v>2.892029656169171</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="1" t="s">
-        <v>27</v>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000010</t>
+        </is>
       </c>
       <c r="B12" t="n">
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>18.48648211040055</v>
+        <v>-6.27770337171313</v>
       </c>
       <c r="D12" t="n">
-        <v>15.29491702411593</v>
-      </c>
-      <c r="E12" t="s">
-        <v>17</v>
+        <v>17.1516042443957</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="1" t="s">
-        <v>28</v>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000011</t>
+        </is>
       </c>
       <c r="B13" t="n">
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>-11.92542118768872</v>
+        <v>-20.20047629867024</v>
       </c>
       <c r="D13" t="n">
-        <v>10.21862605482636</v>
-      </c>
-      <c r="E13" t="s">
-        <v>17</v>
+        <v>5.561129997302558</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F13" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="1" t="s">
-        <v>29</v>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000012</t>
+        </is>
       </c>
       <c r="B14" t="n">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5013583610587204</v>
+        <v>-4.405183536258683</v>
       </c>
       <c r="D14" t="n">
-        <v>15.70475902611797</v>
-      </c>
-      <c r="E14" t="s">
-        <v>17</v>
+        <v>-16.30630999097802</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F14" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="1" t="s">
-        <v>30</v>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000013</t>
+        </is>
       </c>
       <c r="B15" t="n">
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>19.99204617787428</v>
+        <v>8.362068851873993</v>
       </c>
       <c r="D15" t="n">
-        <v>-7.046686921402028</v>
-      </c>
-      <c r="E15" t="s">
-        <v>17</v>
+        <v>15.74665476250709</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F15" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="1" t="s">
-        <v>31</v>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000014</t>
+        </is>
       </c>
       <c r="B16" t="n">
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>-17.01004198513147</v>
+        <v>-19.53790471784319</v>
       </c>
       <c r="D16" t="n">
-        <v>-8.052908250234296</v>
-      </c>
-      <c r="E16" t="s">
-        <v>17</v>
+        <v>-37.91327051785554</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F16" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="1" t="s">
-        <v>32</v>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000015</t>
+        </is>
       </c>
       <c r="B17" t="n">
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>10.41102292794746</v>
+        <v>-9.648506241292552</v>
       </c>
       <c r="D17" t="n">
-        <v>16.89752377037026</v>
-      </c>
-      <c r="E17" t="s">
-        <v>17</v>
+        <v>20.6741258518262</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="1" t="s">
-        <v>33</v>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000016</t>
+        </is>
       </c>
       <c r="B18" t="n">
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>2.631698847571798</v>
+        <v>-11.4477036952264</v>
       </c>
       <c r="D18" t="n">
-        <v>9.069564194801076</v>
-      </c>
-      <c r="E18" t="s">
-        <v>17</v>
+        <v>-60.40516130705608</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F18" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="1" t="s">
-        <v>34</v>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000017</t>
+        </is>
       </c>
       <c r="B19" t="n">
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>-16.4109885128295</v>
+        <v>-26.31476199126989</v>
       </c>
       <c r="D19" t="n">
-        <v>8.665899695735076</v>
-      </c>
-      <c r="E19" t="s">
-        <v>17</v>
+        <v>-80.39164592466346</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F19" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="1" t="s">
-        <v>35</v>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000018</t>
+        </is>
       </c>
       <c r="B20" t="n">
         <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>-16.56110675700298</v>
+        <v>10.02014433115755</v>
       </c>
       <c r="D20" t="n">
-        <v>2.197006845589229</v>
-      </c>
-      <c r="E20" t="s">
-        <v>17</v>
+        <v>-13.19718323932985</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F20" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="1" t="s">
-        <v>36</v>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000019</t>
+        </is>
       </c>
       <c r="B21" t="n">
         <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>-13.57908488015537</v>
+        <v>7.184772037058629</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.234143726252498</v>
-      </c>
-      <c r="E21" t="s">
-        <v>17</v>
+        <v>-8.579212399116415</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F21" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="1" t="s">
-        <v>37</v>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000020</t>
+        </is>
       </c>
       <c r="B22" t="n">
         <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>15.03625410793309</v>
+        <v>8.998294623691571</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.47285004820868</v>
-      </c>
-      <c r="E22" t="s">
-        <v>17</v>
+        <v>15.84856333509967</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F22" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="1" t="s">
-        <v>38</v>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000021</t>
+        </is>
       </c>
       <c r="B23" t="n">
         <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>-10.08081167242276</v>
+        <v>-23.91105477762094</v>
       </c>
       <c r="D23" t="n">
-        <v>14.8457780369409</v>
-      </c>
-      <c r="E23" t="s">
-        <v>17</v>
+        <v>-46.30787927946889</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F23" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="1" t="s">
-        <v>39</v>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000022</t>
+        </is>
       </c>
       <c r="B24" t="n">
         <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>-14.43425957086176</v>
+        <v>11.28179924443845</v>
       </c>
       <c r="D24" t="n">
-        <v>3.052652185257472</v>
-      </c>
-      <c r="E24" t="s">
-        <v>17</v>
+        <v>-2.804777356774906</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F24" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="1" t="s">
-        <v>40</v>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000023</t>
+        </is>
       </c>
       <c r="B25" t="n">
         <v>23</v>
       </c>
       <c r="C25" t="n">
-        <v>-41.90001253276814</v>
+        <v>-24.64055253797792</v>
       </c>
       <c r="D25" t="n">
-        <v>4.380172249458369</v>
-      </c>
-      <c r="E25" t="s">
-        <v>17</v>
+        <v>-80.37709188867042</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F25" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="1" t="s">
-        <v>41</v>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000024</t>
+        </is>
       </c>
       <c r="B26" t="n">
         <v>24</v>
       </c>
       <c r="C26" t="n">
-        <v>-15.23491735759201</v>
+        <v>-3.763921106384585</v>
       </c>
       <c r="D26" t="n">
-        <v>3.800184448019621</v>
-      </c>
-      <c r="E26" t="s">
-        <v>17</v>
+        <v>-38.03588236841014</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F26" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="1" t="s">
-        <v>42</v>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000025</t>
+        </is>
       </c>
       <c r="B27" t="n">
         <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>-39.36137950218873</v>
+        <v>-33.30175507670202</v>
       </c>
       <c r="D27" t="n">
-        <v>6.961533245122182</v>
-      </c>
-      <c r="E27" t="s">
-        <v>17</v>
+        <v>-70.82071031870048</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F27" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="1" t="s">
-        <v>43</v>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000026</t>
+        </is>
       </c>
       <c r="B28" t="n">
         <v>26</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.03259009239693</v>
+        <v>-27.82810081318412</v>
       </c>
       <c r="D28" t="n">
-        <v>-10.10950871589915</v>
-      </c>
-      <c r="E28" t="s">
-        <v>17</v>
+        <v>-13.50904643295175</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F28" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="1" t="s">
-        <v>44</v>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000027</t>
+        </is>
       </c>
       <c r="B29" t="n">
         <v>27</v>
       </c>
       <c r="C29" t="n">
-        <v>-31.92573329309284</v>
+        <v>-12.58403218473581</v>
       </c>
       <c r="D29" t="n">
-        <v>-12.75102662144095</v>
-      </c>
-      <c r="E29" t="s">
-        <v>17</v>
+        <v>28.39290163241324</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F29" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="1" t="s">
-        <v>45</v>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000028</t>
+        </is>
       </c>
       <c r="B30" t="n">
         <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>14.08712021271873</v>
+        <v>-20.095379521502</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5474653959434335</v>
-      </c>
-      <c r="E30" t="s">
-        <v>17</v>
+        <v>-43.25883695604645</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F30" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="1" t="s">
-        <v>46</v>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000029</t>
+        </is>
       </c>
       <c r="B31" t="n">
         <v>29</v>
       </c>
       <c r="C31" t="n">
-        <v>-19.59977597091169</v>
+        <v>2.583740480436333</v>
       </c>
       <c r="D31" t="n">
-        <v>7.802351578417416</v>
-      </c>
-      <c r="E31" t="s">
-        <v>17</v>
+        <v>-31.53931224778795</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F31" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="1" t="s">
-        <v>47</v>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000030</t>
+        </is>
       </c>
       <c r="B32" t="n">
         <v>30</v>
       </c>
       <c r="C32" t="n">
-        <v>9.051791998093172</v>
+        <v>-18.2388313705445</v>
       </c>
       <c r="D32" t="n">
-        <v>-16.17092341658406</v>
-      </c>
-      <c r="E32" t="s">
-        <v>17</v>
+        <v>-12.05808344556891</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F32" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="1" t="s">
-        <v>48</v>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000031</t>
+        </is>
       </c>
       <c r="B33" t="n">
         <v>31</v>
       </c>
       <c r="C33" t="n">
-        <v>-24.24404167657215</v>
+        <v>-16.83531111670868</v>
       </c>
       <c r="D33" t="n">
-        <v>-6.301145860923412</v>
-      </c>
-      <c r="E33" t="s">
-        <v>17</v>
+        <v>-19.77211058132266</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F33" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="1" t="s">
-        <v>49</v>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000032</t>
+        </is>
       </c>
       <c r="B34" t="n">
         <v>32</v>
       </c>
       <c r="C34" t="n">
-        <v>2.862106452276294</v>
+        <v>14.88119226093131</v>
       </c>
       <c r="D34" t="n">
-        <v>-13.81109939610121</v>
-      </c>
-      <c r="E34" t="s">
-        <v>17</v>
+        <v>64.84211012461904</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F34" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="1" t="s">
-        <v>50</v>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000033</t>
+        </is>
       </c>
       <c r="B35" t="n">
         <v>33</v>
       </c>
       <c r="C35" t="n">
-        <v>-38.73014971641683</v>
+        <v>-26.62163483738116</v>
       </c>
       <c r="D35" t="n">
-        <v>-5.842758186235869</v>
-      </c>
-      <c r="E35" t="s">
-        <v>17</v>
+        <v>-87.52811331559116</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="1" t="s">
-        <v>51</v>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000034</t>
+        </is>
       </c>
       <c r="B36" t="n">
         <v>34</v>
       </c>
       <c r="C36" t="n">
-        <v>-23.0117549770495</v>
+        <v>-17.60775163569894</v>
       </c>
       <c r="D36" t="n">
-        <v>-14.86805480118175</v>
-      </c>
-      <c r="E36" t="s">
-        <v>17</v>
+        <v>-98.81377687135289</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F36" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="1" t="s">
-        <v>52</v>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000035</t>
+        </is>
       </c>
       <c r="B37" t="n">
         <v>35</v>
       </c>
       <c r="C37" t="n">
-        <v>-7.586088859036651</v>
+        <v>-1.06316178466907</v>
       </c>
       <c r="D37" t="n">
-        <v>19.73636498681199</v>
-      </c>
-      <c r="E37" t="s">
-        <v>17</v>
+        <v>-48.6900693571238</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F37" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="1" t="s">
-        <v>53</v>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000036</t>
+        </is>
       </c>
       <c r="B38" t="n">
         <v>36</v>
       </c>
       <c r="C38" t="n">
-        <v>8.73789248003942</v>
+        <v>-10.5629002429746</v>
       </c>
       <c r="D38" t="n">
-        <v>8.200762284205453</v>
-      </c>
-      <c r="E38" t="s">
-        <v>17</v>
+        <v>-75.23113504725399</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F38" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="1" t="s">
-        <v>54</v>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000037</t>
+        </is>
       </c>
       <c r="B39" t="n">
         <v>37</v>
       </c>
       <c r="C39" t="n">
-        <v>-40.23807994927729</v>
+        <v>15.5246024713982</v>
       </c>
       <c r="D39" t="n">
-        <v>3.977584805922135</v>
-      </c>
-      <c r="E39" t="s">
-        <v>17</v>
+        <v>-22.55504470794864</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F39" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="1" t="s">
-        <v>55</v>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000038</t>
+        </is>
       </c>
       <c r="B40" t="n">
         <v>38</v>
       </c>
       <c r="C40" t="n">
-        <v>6.735783985791046</v>
+        <v>11.93129420096333</v>
       </c>
       <c r="D40" t="n">
-        <v>-6.521797213862925</v>
-      </c>
-      <c r="E40" t="s">
-        <v>17</v>
+        <v>52.86367675397995</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F40" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="1" t="s">
-        <v>56</v>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000039</t>
+        </is>
       </c>
       <c r="B41" t="n">
         <v>39</v>
       </c>
       <c r="C41" t="n">
-        <v>-32.11547826583482</v>
+        <v>8.604567435911989</v>
       </c>
       <c r="D41" t="n">
-        <v>-7.654971405325099</v>
-      </c>
-      <c r="E41" t="s">
-        <v>17</v>
+        <v>31.07419669192604</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="1" t="s">
-        <v>57</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000040</t>
+        </is>
       </c>
       <c r="B42" t="n">
         <v>40</v>
       </c>
       <c r="C42" t="n">
-        <v>-17.2210854147443</v>
+        <v>21.01143435058023</v>
       </c>
       <c r="D42" t="n">
-        <v>14.37122469349954</v>
-      </c>
-      <c r="E42" t="s">
-        <v>17</v>
+        <v>8.543755436072004</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F42" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="1" t="s">
-        <v>58</v>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000041</t>
+        </is>
       </c>
       <c r="B43" t="n">
         <v>41</v>
       </c>
       <c r="C43" t="n">
-        <v>-35.12251974097423</v>
+        <v>10.18462074713109</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.513590034678785</v>
-      </c>
-      <c r="E43" t="s">
-        <v>17</v>
+        <v>2.9572143122341</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F43" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="1" t="s">
-        <v>59</v>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000042</t>
+        </is>
       </c>
       <c r="B44" t="n">
         <v>42</v>
       </c>
       <c r="C44" t="n">
-        <v>-16.21642663769896</v>
+        <v>4.284343138838985</v>
       </c>
       <c r="D44" t="n">
-        <v>8.592593585022641</v>
-      </c>
-      <c r="E44" t="s">
-        <v>17</v>
+        <v>27.80822025656416</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F44" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="1" t="s">
-        <v>60</v>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000043</t>
+        </is>
       </c>
       <c r="B45" t="n">
         <v>43</v>
       </c>
       <c r="C45" t="n">
-        <v>0.7704114866391123</v>
+        <v>-2.14943166781702</v>
       </c>
       <c r="D45" t="n">
-        <v>21.65364319293591</v>
-      </c>
-      <c r="E45" t="s">
-        <v>17</v>
+        <v>48.71881573148445</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F45" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="1" t="s">
-        <v>61</v>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000044</t>
+        </is>
       </c>
       <c r="B46" t="n">
         <v>44</v>
       </c>
       <c r="C46" t="n">
-        <v>-12.41431378212511</v>
+        <v>-7.158247133262279</v>
       </c>
       <c r="D46" t="n">
-        <v>13.65131719693666</v>
-      </c>
-      <c r="E46" t="s">
-        <v>17</v>
+        <v>17.55786085732835</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F46" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="1" t="s">
-        <v>62</v>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000045</t>
+        </is>
       </c>
       <c r="B47" t="n">
         <v>45</v>
       </c>
       <c r="C47" t="n">
-        <v>-32.95688512640088</v>
+        <v>-13.39330374839685</v>
       </c>
       <c r="D47" t="n">
-        <v>-2.510929373411969</v>
-      </c>
-      <c r="E47" t="s">
-        <v>17</v>
+        <v>-65.44218275626505</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F47" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="1" t="s">
-        <v>63</v>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000046</t>
+        </is>
       </c>
       <c r="B48" t="n">
         <v>46</v>
       </c>
       <c r="C48" t="n">
-        <v>-28.92875655404802</v>
+        <v>19.99427091699709</v>
       </c>
       <c r="D48" t="n">
-        <v>-2.639948799684234</v>
-      </c>
-      <c r="E48" t="s">
-        <v>17</v>
+        <v>-10.54200147556695</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F48" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="1" t="s">
-        <v>64</v>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000047</t>
+        </is>
       </c>
       <c r="B49" t="n">
         <v>47</v>
       </c>
       <c r="C49" t="n">
-        <v>-21.22137915573253</v>
+        <v>0.1399394413221557</v>
       </c>
       <c r="D49" t="n">
-        <v>6.490156678409704</v>
-      </c>
-      <c r="E49" t="s">
-        <v>17</v>
+        <v>-3.974747320603072</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F49" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="1" t="s">
-        <v>65</v>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000048</t>
+        </is>
       </c>
       <c r="B50" t="n">
         <v>48</v>
       </c>
       <c r="C50" t="n">
-        <v>-25.43299411658989</v>
+        <v>-22.44362981468714</v>
       </c>
       <c r="D50" t="n">
-        <v>-14.98760651516247</v>
-      </c>
-      <c r="E50" t="s">
-        <v>17</v>
+        <v>-34.43189275286149</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F50" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="1" t="s">
-        <v>66</v>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000049</t>
+        </is>
       </c>
       <c r="B51" t="n">
         <v>49</v>
       </c>
       <c r="C51" t="n">
-        <v>-6.904847289375829</v>
+        <v>-11.23729039111512</v>
       </c>
       <c r="D51" t="n">
-        <v>-18.4307280362564</v>
-      </c>
-      <c r="E51" t="s">
-        <v>17</v>
+        <v>14.3795995822688</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F51" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="1" t="s">
-        <v>67</v>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000050</t>
+        </is>
       </c>
       <c r="B52" t="n">
         <v>50</v>
       </c>
       <c r="C52" t="n">
-        <v>-27.82371049578684</v>
+        <v>-6.316601629299115</v>
       </c>
       <c r="D52" t="n">
-        <v>4.827542519883039</v>
-      </c>
-      <c r="E52" t="s">
-        <v>17</v>
+        <v>-55.15468806373981</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F52" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="1" t="s">
-        <v>68</v>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000051</t>
+        </is>
       </c>
       <c r="B53" t="n">
         <v>51</v>
       </c>
       <c r="C53" t="n">
-        <v>11.39004839295535</v>
+        <v>-8.177017009087358</v>
       </c>
       <c r="D53" t="n">
-        <v>-17.05978737646872</v>
-      </c>
-      <c r="E53" t="s">
-        <v>17</v>
+        <v>-63.78566414061727</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F53" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="1" t="s">
-        <v>69</v>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000052</t>
+        </is>
       </c>
       <c r="B54" t="n">
         <v>52</v>
       </c>
       <c r="C54" t="n">
-        <v>-1.471629036094555</v>
+        <v>-37.9931902790291</v>
       </c>
       <c r="D54" t="n">
-        <v>15.13391593356201</v>
-      </c>
-      <c r="E54" t="s">
-        <v>17</v>
+        <v>-61.65903397512691</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
       </c>
       <c r="F54" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000053</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>53</v>
+      </c>
+      <c r="C55" t="n">
+        <v>13.54336670365466</v>
+      </c>
+      <c r="D55" t="n">
+        <v>24.46980731380361</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056</t>
+        </is>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1763,605 +1880,730 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sample_Id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sim_Id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sim_Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000000</t>
+        </is>
       </c>
       <c r="B2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>24.39657166015621</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>26.63434037606872</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000001</t>
+        </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>13.80479329737066</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>35.51564267423782</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000002</t>
+        </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>29.06326999105486</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>64.94620275194954</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000003</t>
+        </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>41.37719807629199</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>44.5469656170439</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000004</t>
+        </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>11.82669292832045</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>48.85685492685199</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000005</t>
+        </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>21.20510405537468</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>45.13575522793813</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000006</t>
+        </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>13.60611410555557</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>53.12589551522951</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000007</t>
+        </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>8.314140081022504</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>76.44080926165928</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000008</t>
+        </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>37.41704469074293</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>33.20344915336793</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000009</t>
+        </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>30.61111626339154</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>3.274008139771791</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000010</t>
+        </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0180734590077</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>17.4905797043102</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000011</t>
+        </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>15.35250593084126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>21.31728755274432</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000012</t>
+        </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>15.1563257919741</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>16.58694422929718</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000013</t>
+        </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>21.87083661879726</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>19.22480047493128</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000014</t>
+        </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>18.31428826135992</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="1" t="s">
-        <v>32</v>
+        <v>43.0317586847402</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000015</t>
+        </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>18.27964309771316</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="1" t="s">
-        <v>33</v>
+        <v>23.87445088020447</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000016</t>
+        </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>8.956569567739871</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="1" t="s">
-        <v>34</v>
+        <v>61.89038208278277</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000017</t>
+        </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>17.76907477084569</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1" t="s">
-        <v>35</v>
+        <v>84.11272164973398</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000018</t>
+        </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>15.44282323516243</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="1" t="s">
-        <v>36</v>
+        <v>17.38739496583452</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000019</t>
+        </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>14.12954167972452</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="1" t="s">
-        <v>37</v>
+        <v>10.45878034356154</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000020</t>
+        </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>17.05142185515759</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="1" t="s">
-        <v>38</v>
+        <v>17.5619835782877</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000021</t>
+        </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>17.58896809499064</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="1" t="s">
-        <v>39</v>
+        <v>51.57147420674121</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000022</t>
+        </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>15.54489676727618</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="1" t="s">
-        <v>40</v>
+        <v>11.21921832064301</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000023</t>
+        </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C25" t="n">
-        <v>42.48642379401265</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="1" t="s">
-        <v>41</v>
+        <v>84.15113225510866</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000024</t>
+        </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>24</v>
       </c>
       <c r="C26" t="n">
-        <v>15.91015344265877</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="1" t="s">
-        <v>42</v>
+        <v>40.28841083144066</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000025</t>
+        </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>39.75574010138832</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="1" t="s">
-        <v>43</v>
+        <v>80.17968680495362</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000026</t>
+        </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C28" t="n">
-        <v>11.20376454891801</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="1" t="s">
-        <v>44</v>
+        <v>32.89180539739159</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000027</t>
+        </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C29" t="n">
-        <v>34.05021306630596</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="1" t="s">
-        <v>45</v>
+        <v>31.57540632839996</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000028</t>
+        </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>14.88883877769784</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="1" t="s">
-        <v>46</v>
+        <v>47.12336059198014</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000029</t>
+        </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>29</v>
       </c>
       <c r="C31" t="n">
-        <v>21.21903935697876</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="1" t="s">
-        <v>47</v>
+        <v>32.80000479133395</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000030</t>
+        </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>30</v>
       </c>
       <c r="C32" t="n">
-        <v>18.07399724949116</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>20.50254513143411</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000031</t>
+        </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>31</v>
       </c>
       <c r="C33" t="n">
-        <v>26.06599532052696</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="1" t="s">
-        <v>49</v>
+        <v>27.60438072906973</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000032</t>
+        </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>32</v>
       </c>
       <c r="C34" t="n">
-        <v>15.64820377908749</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>65.82765074529068</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000033</t>
+        </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>33</v>
       </c>
       <c r="C35" t="n">
-        <v>38.298758685184</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="1" t="s">
-        <v>51</v>
+        <v>91.55056506467018</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000034</t>
+        </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>34</v>
       </c>
       <c r="C36" t="n">
-        <v>27.26949600921141</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="1" t="s">
-        <v>52</v>
+        <v>100.0249168536384</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000035</t>
+        </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>35</v>
       </c>
       <c r="C37" t="n">
-        <v>20.18005974625354</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="1" t="s">
-        <v>53</v>
+        <v>48.07394190275413</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000036</t>
+        </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>36</v>
       </c>
       <c r="C38" t="n">
-        <v>11.58475745145461</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="1" t="s">
-        <v>54</v>
+        <v>77.64031695799386</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000037</t>
+        </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>37</v>
       </c>
       <c r="C39" t="n">
-        <v>40.1961231578856</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="1" t="s">
-        <v>55</v>
+        <v>30.06293449465939</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000038</t>
+        </is>
       </c>
       <c r="B40" s="1" t="n">
         <v>38</v>
       </c>
       <c r="C40" t="n">
-        <v>10.44754326885495</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="1" t="s">
-        <v>56</v>
+        <v>54.19527270240025</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000039</t>
+        </is>
       </c>
       <c r="B41" s="1" t="n">
         <v>39</v>
       </c>
       <c r="C41" t="n">
-        <v>32.73994135871285</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="1" t="s">
-        <v>57</v>
+        <v>31.57322286770835</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000040</t>
+        </is>
       </c>
       <c r="B42" s="1" t="n">
         <v>40</v>
       </c>
       <c r="C42" t="n">
-        <v>21.09146970262135</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="1" t="s">
-        <v>58</v>
+        <v>23.27872781122083</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000041</t>
+        </is>
       </c>
       <c r="B43" s="1" t="n">
         <v>41</v>
       </c>
       <c r="C43" t="n">
-        <v>37.1835025800134</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="1" t="s">
-        <v>59</v>
+        <v>9.773947340101488</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000042</t>
+        </is>
       </c>
       <c r="B44" s="1" t="n">
         <v>42</v>
       </c>
       <c r="C44" t="n">
-        <v>18.40345657952444</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="1" t="s">
-        <v>60</v>
+        <v>28.54562602282203</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000043</t>
+        </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>43</v>
       </c>
       <c r="C45" t="n">
-        <v>21.85086396069195</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="1" t="s">
-        <v>61</v>
+        <v>49.34737797215114</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000044</t>
+        </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44</v>
       </c>
       <c r="C46" t="n">
-        <v>18.54654793798706</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="1" t="s">
-        <v>62</v>
+        <v>18.97539021148032</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000045</t>
+        </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>45</v>
       </c>
       <c r="C47" t="n">
-        <v>32.63951692735998</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="1" t="s">
-        <v>63</v>
+        <v>65.58128792514617</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000046</t>
+        </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>46</v>
       </c>
       <c r="C48" t="n">
-        <v>29.56602724456997</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="1" t="s">
-        <v>64</v>
+        <v>24.64367486257672</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000047</t>
+        </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>47</v>
       </c>
       <c r="C49" t="n">
-        <v>21.15111311044681</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="1" t="s">
-        <v>65</v>
+        <v>1.472633218285403</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000048</t>
+        </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>48</v>
       </c>
       <c r="C50" t="n">
-        <v>31.47507357129949</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="1" t="s">
-        <v>66</v>
+        <v>41.78195574572739</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000049</t>
+        </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>49</v>
       </c>
       <c r="C51" t="n">
-        <v>20.56889095849385</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="1" t="s">
-        <v>67</v>
+        <v>16.77486893127862</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000050</t>
+        </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>50</v>
       </c>
       <c r="C52" t="n">
-        <v>30.63957559157354</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="1" t="s">
-        <v>68</v>
+        <v>55.82934642671849</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000051</t>
+        </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>51</v>
       </c>
       <c r="C53" t="n">
-        <v>20.64054628935165</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="1" t="s">
-        <v>69</v>
+        <v>64.34600955865722</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000052</t>
+        </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>52</v>
       </c>
       <c r="C54" t="n">
-        <v>15.33346870870436</v>
+        <v>70.91951094807814</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>Data_20220831_143056.000053</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="C55" t="n">
+        <v>29.06080648090117</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2374,20 +2616,28 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>12</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>First Parameter</t>
+        </is>
       </c>
       <c r="B2" t="n">
         <v>-50</v>
@@ -2396,9 +2646,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Second Parameter</t>
+        </is>
       </c>
       <c r="B3" t="n">
         <v>-100</v>
@@ -2408,6 +2660,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>